--- a/evac_by_zip/evac_by_zip_2026-08-23.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-23.xlsx
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 269 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 294 addresses (across 4 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -740,20 +740,20 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>429</v>
+        <v>294</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -762,32 +762,32 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -796,32 +796,32 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -830,32 +830,32 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -864,32 +864,32 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -898,32 +898,32 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -942,92 +942,94 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>84</v>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <v>5</v>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -1036,7 +1038,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1048,7 +1050,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>97023</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -1060,11 +1062,11 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Level 3</t>
@@ -1072,7 +1074,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1082,38 +1084,38 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>171</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>256</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>No named fire</t>
+      <c r="E17" s="10" t="n">
+        <v>427</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
     </row>
@@ -1458,16 +1460,16 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>2836</v>
+        <v>2844</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4332</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="29">
@@ -1477,16 +1479,16 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>269</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30">
@@ -1496,16 +1498,16 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>3035</v>
+        <v>3068</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>1170</v>
+        <v>1202</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>396</v>
+        <v>354</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>4601</v>
+        <v>4624</v>
       </c>
     </row>
   </sheetData>
@@ -1523,7 +1525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3752,22 +3754,22 @@
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SB</t>
+          <t>US-OR-KLA-FHZ-1166</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E65" s="21" t="inlineStr">
@@ -3777,32 +3779,32 @@
       </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G65" s="21" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC</t>
+          <t>US-OR-KLA-FHZ-1582-A</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E66" s="21" t="inlineStr">
@@ -3812,32 +3814,32 @@
       </c>
       <c r="F66" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="G66" s="21" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-A</t>
+          <t>US-OR-KLA-KLA-1162</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E67" s="21" t="inlineStr">
@@ -3847,7 +3849,7 @@
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G67" s="21" t="n">
@@ -3855,164 +3857,164 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B68" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-D</t>
-        </is>
-      </c>
-      <c r="C68" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D68" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E68" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F68" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G68" s="25" t="n">
-        <v>62</v>
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1167</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E68" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B69" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4SK-C</t>
-        </is>
-      </c>
-      <c r="C69" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D69" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E69" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F69" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G69" s="25" t="n">
-        <v>34</v>
+      <c r="A69" s="21" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1165-B</t>
+        </is>
+      </c>
+      <c r="C69" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E69" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B70" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-O</t>
-        </is>
-      </c>
-      <c r="C70" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D70" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E70" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F70" s="25" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="G70" s="25" t="n">
-        <v>21</v>
+      <c r="A70" s="21" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1381-B</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E70" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B71" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-L</t>
-        </is>
-      </c>
-      <c r="C71" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D71" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E71" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F71" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G71" s="25" t="n">
-        <v>18</v>
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1381-C</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E71" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G71" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B72" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC-A</t>
+          <t>US-OR-KLA-KLA-1165-A</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D72" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E72" s="25" t="inlineStr">
@@ -4026,28 +4028,28 @@
         </is>
       </c>
       <c r="G72" s="25" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-I</t>
+          <t>US-OR-KLA-FHZ-1581-A</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D73" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E73" s="25" t="inlineStr">
@@ -4067,22 +4069,22 @@
     <row r="74">
       <c r="A74" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B74" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-K</t>
+          <t>US-OR-KLA-KLA-1156</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D74" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E74" s="25" t="inlineStr">
@@ -4092,32 +4094,32 @@
       </c>
       <c r="F74" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G74" s="25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC-B</t>
+          <t>US-OR-KLA-KLA-1381-A</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D75" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E75" s="25" t="inlineStr">
@@ -4127,7 +4129,7 @@
       </c>
       <c r="F75" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G75" s="25" t="n">
@@ -4137,22 +4139,22 @@
     <row r="76">
       <c r="A76" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B76" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-C</t>
+          <t>US-OR-KLA-KLA-1161</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D76" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E76" s="25" t="inlineStr">
@@ -4166,28 +4168,28 @@
         </is>
       </c>
       <c r="G76" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B77" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-T</t>
+          <t>US-OR-KLA-FHZ-1582-C</t>
         </is>
       </c>
       <c r="C77" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D77" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E77" s="25" t="inlineStr">
@@ -4201,28 +4203,28 @@
         </is>
       </c>
       <c r="G77" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B78" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-F</t>
+          <t>US-OR-KLA-KLA-1168-A</t>
         </is>
       </c>
       <c r="C78" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D78" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E78" s="25" t="inlineStr">
@@ -4236,28 +4238,28 @@
         </is>
       </c>
       <c r="G78" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-J</t>
+          <t>US-OR-KLA-FHZ-1582-B</t>
         </is>
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D79" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E79" s="25" t="inlineStr">
@@ -4267,32 +4269,32 @@
       </c>
       <c r="F79" s="25" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G79" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B80" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-S</t>
+          <t>US-OR-KLA-KLA-1164-B</t>
         </is>
       </c>
       <c r="C80" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D80" s="26" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E80" s="25" t="inlineStr">
@@ -4302,312 +4304,312 @@
       </c>
       <c r="F80" s="25" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G80" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1176</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E81" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1416</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1171</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E83" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1031</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E84" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1401</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E85" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1391</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-FHZ-1583</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B81" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-N</t>
-        </is>
-      </c>
-      <c r="C81" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D81" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E81" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F81" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G81" s="25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B82" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4SB-G</t>
-        </is>
-      </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E82" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F82" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G82" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B83" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-I</t>
-        </is>
-      </c>
-      <c r="C83" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D83" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E83" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F83" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G83" s="25" t="n">
+    <row r="88">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1361</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E88" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B84" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4SK-B</t>
-        </is>
-      </c>
-      <c r="C84" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D84" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E84" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F84" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G84" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B85" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-1S-Q</t>
-        </is>
-      </c>
-      <c r="C85" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D85" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E85" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F85" s="25" t="inlineStr">
-        <is>
-          <t>13%</t>
-        </is>
-      </c>
-      <c r="G85" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B86" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-M</t>
-        </is>
-      </c>
-      <c r="C86" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D86" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E86" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F86" s="25" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G86" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B87" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-I</t>
-        </is>
-      </c>
-      <c r="C87" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D87" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E87" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F87" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G87" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B88" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-E</t>
-        </is>
-      </c>
-      <c r="C88" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D88" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E88" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F88" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G88" s="25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="23" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-F</t>
+          <t>US-OR-KLA-KLA-1386</t>
         </is>
       </c>
       <c r="C89" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D89" s="24" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
@@ -4617,32 +4619,32 @@
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G89" s="23" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="23" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-J</t>
+          <t>US-OR-KLA-KLA-1371</t>
         </is>
       </c>
       <c r="C90" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D90" s="24" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -4652,207 +4654,207 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G90" s="23" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="23" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B91" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-1S-J</t>
-        </is>
-      </c>
-      <c r="C91" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D91" s="24" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E91" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="n">
-        <v>25</v>
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-McCullyForkHeadwaters</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="23" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B92" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-1S-K</t>
-        </is>
-      </c>
-      <c r="C92" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D92" s="24" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="n">
-        <v>25</v>
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1246</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F92" s="21" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G92" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="23" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B93" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-1S-F</t>
-        </is>
-      </c>
-      <c r="C93" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D93" s="24" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E93" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F93" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="n">
-        <v>15</v>
+      <c r="A93" s="21" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1247</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E93" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="23" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B94" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8SG-B</t>
-        </is>
-      </c>
-      <c r="C94" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D94" s="24" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E94" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F94" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="n">
-        <v>7</v>
+      <c r="A94" s="25" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B94" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-636</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E94" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F94" s="25" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="G94" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="23" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B95" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4SB-D</t>
-        </is>
-      </c>
-      <c r="C95" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D95" s="24" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E95" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F95" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="n">
-        <v>4</v>
+      <c r="A95" s="25" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B95" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1347</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D95" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E95" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F95" s="25" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G95" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="23" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-M</t>
+          <t>US-OR-BAK-SMT-600</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D96" s="24" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
@@ -4866,28 +4868,28 @@
         </is>
       </c>
       <c r="G96" s="23" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-E</t>
+          <t>US-OR-BAK-SMT-610</t>
         </is>
       </c>
       <c r="C97" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D97" s="24" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -4901,28 +4903,28 @@
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="23" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-N</t>
+          <t>US-OR-BAK-SMT-632</t>
         </is>
       </c>
       <c r="C98" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D98" s="24" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
@@ -4932,102 +4934,102 @@
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="G98" s="23" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="23" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B99" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-Q</t>
-        </is>
-      </c>
-      <c r="C99" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D99" s="24" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E99" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F99" s="23" t="inlineStr">
-        <is>
-          <t>61%</t>
-        </is>
-      </c>
-      <c r="G99" s="23" t="n">
-        <v>1</v>
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E99" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G99" s="21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="23" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B100" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-G</t>
-        </is>
-      </c>
-      <c r="C100" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D100" s="24" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E100" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F100" s="23" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="G100" s="23" t="n">
-        <v>1</v>
+      <c r="A100" s="25" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B100" s="26" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D100" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E100" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F100" s="25" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="G100" s="25" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="23" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-090-A</t>
+          <t>HH</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D101" s="24" t="inlineStr">
         <is>
-          <t>Crook, Wheeler</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -5037,407 +5039,407 @@
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="23" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D102" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F102" s="23" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="23" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B103" s="24" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D103" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="23" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>WRR</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D104" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F104" s="23" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="23" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D105" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="23" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F106" s="23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="inlineStr">
+        <is>
+          <t>SCH</t>
+        </is>
+      </c>
+      <c r="C107" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E107" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="23" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D108" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E108" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F108" s="23" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1381-C</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E109" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="G109" s="21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1381-B</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E110" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="G110" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-FHZ-1582-A</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E111" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G101" s="23" t="n">
+      <c r="G111" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="21" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B102" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1166</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="21" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1167</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D102" s="22" t="inlineStr">
+      <c r="D112" s="22" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E102" s="21" t="inlineStr">
+      <c r="E112" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F102" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G102" s="21" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="21" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B103" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1582-A</t>
-        </is>
-      </c>
-      <c r="C103" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D103" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E103" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F103" s="21" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="G103" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B104" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1162</t>
-        </is>
-      </c>
-      <c r="C104" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D104" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E104" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G104" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B105" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1167</t>
-        </is>
-      </c>
-      <c r="C105" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D105" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E105" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="G105" s="21" t="n">
+      <c r="F112" s="21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G112" s="21" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="21" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B106" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1165-B</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D106" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E106" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G106" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="21" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B107" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
-        </is>
-      </c>
-      <c r="C107" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D107" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E107" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F107" s="21" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="G107" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="21" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B108" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-C</t>
-        </is>
-      </c>
-      <c r="C108" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D108" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E108" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F108" s="21" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G108" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="25" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B109" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1165-A</t>
-        </is>
-      </c>
-      <c r="C109" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D109" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E109" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F109" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G109" s="25" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="25" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B110" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1581-A</t>
-        </is>
-      </c>
-      <c r="C110" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D110" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E110" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F110" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G110" s="25" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="25" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B111" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1156</t>
-        </is>
-      </c>
-      <c r="C111" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D111" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E111" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F111" s="25" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="G111" s="25" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="25" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B112" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-A</t>
-        </is>
-      </c>
-      <c r="C112" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D112" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E112" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F112" s="25" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G112" s="25" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="25" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B113" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1161</t>
+          <t>US-OR-KLA-KLA-1396</t>
         </is>
       </c>
       <c r="C113" s="26" t="inlineStr">
@@ -5461,18 +5463,18 @@
         </is>
       </c>
       <c r="G113" s="25" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="25" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B114" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1582-C</t>
+          <t>US-OR-KLA-KLA-1381-A</t>
         </is>
       </c>
       <c r="C114" s="26" t="inlineStr">
@@ -5492,22 +5494,22 @@
       </c>
       <c r="F114" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G114" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="25" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B115" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1168-A</t>
+          <t>US-OR-KLA-KLA-1717</t>
         </is>
       </c>
       <c r="C115" s="26" t="inlineStr">
@@ -5527,92 +5529,92 @@
       </c>
       <c r="F115" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G115" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="25" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B116" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1582-B</t>
-        </is>
-      </c>
-      <c r="C116" s="26" t="inlineStr">
+      <c r="A116" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1386</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D116" s="26" t="inlineStr">
+      <c r="D116" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E116" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F116" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G116" s="25" t="n">
-        <v>2</v>
+      <c r="E116" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F116" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G116" s="23" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="25" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B117" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1164-B</t>
-        </is>
-      </c>
-      <c r="C117" s="26" t="inlineStr">
+      <c r="A117" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1426</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D117" s="26" t="inlineStr">
+      <c r="D117" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E117" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F117" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G117" s="25" t="n">
-        <v>2</v>
+      <c r="E117" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="23" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1176</t>
+          <t>US-OR-KLA-FHZ-1583</t>
         </is>
       </c>
       <c r="C118" s="24" t="inlineStr">
@@ -5632,22 +5634,22 @@
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="G118" s="23" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="23" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1416</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C119" s="24" t="inlineStr">
@@ -5667,22 +5669,22 @@
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="23" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1171</t>
+          <t>US-OR-KLA-KLA-1371</t>
         </is>
       </c>
       <c r="C120" s="24" t="inlineStr">
@@ -5702,22 +5704,22 @@
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G120" s="23" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1031</t>
+          <t>US-OR-KLA-KLA-1431</t>
         </is>
       </c>
       <c r="C121" s="24" t="inlineStr">
@@ -5737,22 +5739,22 @@
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="23" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1401</t>
+          <t>US-OR-KLA-KLA-1718-A</t>
         </is>
       </c>
       <c r="C122" s="24" t="inlineStr">
@@ -5772,22 +5774,22 @@
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="G122" s="23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="23" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1391</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C123" s="24" t="inlineStr">
@@ -5807,22 +5809,22 @@
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G123" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="23" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1583</t>
+          <t>US-OR-KLA-KLA-1718-B</t>
         </is>
       </c>
       <c r="C124" s="24" t="inlineStr">
@@ -5842,127 +5844,127 @@
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G124" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="23" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B125" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1361</t>
-        </is>
-      </c>
-      <c r="C125" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D125" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E125" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F125" s="23" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="G125" s="23" t="n">
-        <v>2</v>
+      <c r="A125" s="21" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B125" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406017-A</t>
+        </is>
+      </c>
+      <c r="C125" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E125" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G125" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="23" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B126" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1386</t>
-        </is>
-      </c>
-      <c r="C126" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D126" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E126" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F126" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G126" s="23" t="n">
-        <v>1</v>
+      <c r="A126" s="21" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406053-C</t>
+        </is>
+      </c>
+      <c r="C126" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E126" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G126" s="21" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="23" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1371</t>
-        </is>
-      </c>
-      <c r="C127" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D127" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E127" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F127" s="23" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G127" s="23" t="n">
-        <v>1</v>
+      <c r="A127" s="21" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B127" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-151-D</t>
+        </is>
+      </c>
+      <c r="C127" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E127" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="G127" s="21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="21" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B128" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-McCullyForkHeadwaters</t>
+          <t>US-OR-UMA-UMC-153</t>
         </is>
       </c>
       <c r="C128" s="22" t="inlineStr">
@@ -5972,7 +5974,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E128" s="21" t="inlineStr">
@@ -5982,7 +5984,7 @@
       </c>
       <c r="F128" s="21" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G128" s="21" t="n">
@@ -5992,12 +5994,12 @@
     <row r="129">
       <c r="A129" s="21" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B129" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1246</t>
+          <t>US-OR-UMA-UMC-1406015-A</t>
         </is>
       </c>
       <c r="C129" s="22" t="inlineStr">
@@ -6007,7 +6009,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -6017,22 +6019,22 @@
       </c>
       <c r="F129" s="21" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G129" s="21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="21" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B130" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1247</t>
+          <t>US-OR-UMA-UMC-1406053-B</t>
         </is>
       </c>
       <c r="C130" s="22" t="inlineStr">
@@ -6042,7 +6044,7 @@
       </c>
       <c r="D130" s="22" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E130" s="21" t="inlineStr">
@@ -6052,7 +6054,7 @@
       </c>
       <c r="F130" s="21" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G130" s="21" t="n">
@@ -6060,49 +6062,49 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B131" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-636</t>
-        </is>
-      </c>
-      <c r="C131" s="26" t="inlineStr">
+      <c r="A131" s="21" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B131" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-155-B</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D131" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E131" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F131" s="25" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="G131" s="25" t="n">
+      <c r="D131" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E131" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G131" s="21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="25" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B132" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1347</t>
+          <t>US-OR-UMA-UMC-1406015-E</t>
         </is>
       </c>
       <c r="C132" s="26" t="inlineStr">
@@ -6112,7 +6114,7 @@
       </c>
       <c r="D132" s="26" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E132" s="25" t="inlineStr">
@@ -6122,172 +6124,172 @@
       </c>
       <c r="F132" s="25" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G132" s="25" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="23" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B133" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-600</t>
-        </is>
-      </c>
-      <c r="C133" s="24" t="inlineStr">
+      <c r="A133" s="25" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B133" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-E</t>
+        </is>
+      </c>
+      <c r="C133" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D133" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E133" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F133" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G133" s="23" t="n">
-        <v>115</v>
+      <c r="D133" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E133" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F133" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G133" s="25" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="23" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B134" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-610</t>
-        </is>
-      </c>
-      <c r="C134" s="24" t="inlineStr">
+      <c r="A134" s="25" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B134" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-D</t>
+        </is>
+      </c>
+      <c r="C134" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D134" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E134" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F134" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G134" s="23" t="n">
-        <v>102</v>
+      <c r="D134" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E134" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F134" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G134" s="25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="23" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B135" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-632</t>
-        </is>
-      </c>
-      <c r="C135" s="24" t="inlineStr">
+      <c r="A135" s="25" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B135" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C135" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D135" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E135" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F135" s="23" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="n">
-        <v>22</v>
+      <c r="D135" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E135" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F135" s="25" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G135" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="21" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B136" s="22" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C136" s="22" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D136" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E136" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F136" s="21" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G136" s="21" t="n">
+      <c r="A136" s="25" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B136" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406015-C</t>
+        </is>
+      </c>
+      <c r="C136" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D136" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E136" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F136" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G136" s="25" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="25" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B137" s="26" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>US-OR-UMA-UMC-149-B</t>
         </is>
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D137" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -6297,32 +6299,32 @@
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="G137" s="25" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="23" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>HH</t>
+          <t>US-OR-UMA-UMC-215-C</t>
         </is>
       </c>
       <c r="C138" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D138" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
@@ -6336,28 +6338,28 @@
         </is>
       </c>
       <c r="G138" s="23" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="23" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>US-OR-UMA-UMC-215-F</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D139" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
@@ -6367,32 +6369,32 @@
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G139" s="23" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="23" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>US-OR-UMA-UMC-151-G</t>
         </is>
       </c>
       <c r="C140" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D140" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
@@ -6402,102 +6404,102 @@
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G140" s="23" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="23" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B141" s="24" t="inlineStr">
-        <is>
-          <t>WRR</t>
-        </is>
-      </c>
-      <c r="C141" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D141" s="24" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E141" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F141" s="23" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="G141" s="23" t="n">
-        <v>19</v>
+      <c r="A141" s="21" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B141" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406043-C</t>
+        </is>
+      </c>
+      <c r="C141" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E141" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G141" s="21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="23" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B142" s="24" t="inlineStr">
-        <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="C142" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D142" s="24" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E142" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F142" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G142" s="23" t="n">
-        <v>18</v>
+      <c r="A142" s="25" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B142" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C142" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D142" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E142" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F142" s="25" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G142" s="25" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="23" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>US-OR-UMA-UMC-032</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D143" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
@@ -6507,522 +6509,522 @@
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="G143" s="23" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="23" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B144" s="24" t="inlineStr">
-        <is>
-          <t>SCH</t>
-        </is>
-      </c>
-      <c r="C144" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D144" s="24" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E144" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F144" s="23" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="G144" s="23" t="n">
-        <v>2</v>
+      <c r="A144" s="21" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1713-B</t>
+        </is>
+      </c>
+      <c r="C144" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E144" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F144" s="21" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G144" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="23" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B145" s="24" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C145" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D145" s="24" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E145" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F145" s="23" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="G145" s="23" t="n">
+      <c r="A145" s="21" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B145" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1713-A</t>
+        </is>
+      </c>
+      <c r="C145" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E145" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G145" s="21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B146" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-C</t>
-        </is>
-      </c>
-      <c r="C146" s="22" t="inlineStr">
+      <c r="A146" s="25" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B146" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1707</t>
+        </is>
+      </c>
+      <c r="C146" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D146" s="22" t="inlineStr">
+      <c r="D146" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E146" s="21" t="inlineStr">
+      <c r="E146" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F146" s="25" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="G146" s="25" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="25" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B147" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1941</t>
+        </is>
+      </c>
+      <c r="C147" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D147" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E147" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F147" s="25" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="G147" s="25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="25" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B148" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1956</t>
+        </is>
+      </c>
+      <c r="C148" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D148" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E148" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F148" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G148" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="23" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B149" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2261</t>
+        </is>
+      </c>
+      <c r="C149" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D149" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E149" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F149" s="23" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G149" s="23" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="23" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B150" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1946</t>
+        </is>
+      </c>
+      <c r="C150" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D150" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E150" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F150" s="23" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G150" s="23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="23" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B151" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1701</t>
+        </is>
+      </c>
+      <c r="C151" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D151" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E151" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F151" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="23" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B152" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1361</t>
+        </is>
+      </c>
+      <c r="C152" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D152" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E152" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F152" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B153" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140618N</t>
+        </is>
+      </c>
+      <c r="C153" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E153" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F146" s="21" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="G146" s="21" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B147" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
-        </is>
-      </c>
-      <c r="C147" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D147" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E147" s="21" t="inlineStr">
+      <c r="F153" s="21" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G153" s="21" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B154" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140624S</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E154" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F147" s="21" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="G147" s="21" t="n">
+      <c r="F154" s="21" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="G154" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B148" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1582-A</t>
-        </is>
-      </c>
-      <c r="C148" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D148" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E148" s="21" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B155" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406024A</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D155" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E155" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F148" s="21" t="inlineStr">
+      <c r="F155" s="21" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G148" s="21" t="n">
+      <c r="G155" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B149" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1167</t>
-        </is>
-      </c>
-      <c r="C149" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D149" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E149" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F149" s="21" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="25" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B156" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140624N-B</t>
+        </is>
+      </c>
+      <c r="C156" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D156" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E156" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F156" s="25" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G156" s="25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="25" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B157" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406030-A</t>
+        </is>
+      </c>
+      <c r="C157" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D157" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E157" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F157" s="25" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G149" s="21" t="n">
+      <c r="G157" s="25" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="25" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B150" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1396</t>
-        </is>
-      </c>
-      <c r="C150" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D150" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E150" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F150" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G150" s="25" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="25" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B151" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-A</t>
-        </is>
-      </c>
-      <c r="C151" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D151" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E151" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F151" s="25" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="G151" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="25" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B152" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1717</t>
-        </is>
-      </c>
-      <c r="C152" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D152" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E152" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F152" s="25" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G152" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="23" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B153" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1386</t>
-        </is>
-      </c>
-      <c r="C153" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D153" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E153" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F153" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="23" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B154" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1426</t>
-        </is>
-      </c>
-      <c r="C154" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D154" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E154" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F154" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G154" s="23" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="23" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B155" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1583</t>
-        </is>
-      </c>
-      <c r="C155" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D155" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E155" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F155" s="23" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="G155" s="23" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="23" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B156" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1566</t>
-        </is>
-      </c>
-      <c r="C156" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D156" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E156" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F156" s="23" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="G156" s="23" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="23" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B157" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1371</t>
-        </is>
-      </c>
-      <c r="C157" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D157" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E157" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F157" s="23" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="G157" s="23" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="23" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1431</t>
+          <t>US-OR-UNI-UCO-1497</t>
         </is>
       </c>
       <c r="C158" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D158" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
@@ -7032,32 +7034,32 @@
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G158" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="23" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1718-A</t>
+          <t>US-OR-UNI-UCO-1505</t>
         </is>
       </c>
       <c r="C159" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D159" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
@@ -7067,7 +7069,7 @@
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G159" s="23" t="n">
@@ -7077,22 +7079,22 @@
     <row r="160">
       <c r="A160" s="23" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-UNI-UCO-1513</t>
         </is>
       </c>
       <c r="C160" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D160" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
@@ -7102,7 +7104,7 @@
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G160" s="23" t="n">
@@ -7112,22 +7114,22 @@
     <row r="161">
       <c r="A161" s="23" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B161" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1718-B</t>
+          <t>US-OR-UNI-UCO-1495</t>
         </is>
       </c>
       <c r="C161" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D161" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
@@ -7137,7 +7139,7 @@
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G161" s="23" t="n">
@@ -7147,12 +7149,12 @@
     <row r="162">
       <c r="A162" s="21" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B162" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C162" s="22" t="inlineStr">
@@ -7162,7 +7164,7 @@
       </c>
       <c r="D162" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E162" s="21" t="inlineStr">
@@ -7172,57 +7174,57 @@
       </c>
       <c r="F162" s="21" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G162" s="21" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="21" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B163" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-C</t>
-        </is>
-      </c>
-      <c r="C163" s="22" t="inlineStr">
+      <c r="A163" s="23" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B163" s="24" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C163" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D163" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E163" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F163" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G163" s="21" t="n">
-        <v>16</v>
+      <c r="D163" s="24" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E163" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F163" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="21" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B164" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-BAK-BAB-1247</t>
         </is>
       </c>
       <c r="C164" s="22" t="inlineStr">
@@ -7232,7 +7234,7 @@
       </c>
       <c r="D164" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E164" s="21" t="inlineStr">
@@ -7246,18 +7248,18 @@
         </is>
       </c>
       <c r="G164" s="21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="21" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B165" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-153</t>
+          <t>US-OR-BAK-BAB-1246</t>
         </is>
       </c>
       <c r="C165" s="22" t="inlineStr">
@@ -7267,7 +7269,7 @@
       </c>
       <c r="D165" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E165" s="21" t="inlineStr">
@@ -7277,172 +7279,172 @@
       </c>
       <c r="F165" s="21" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G165" s="21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="21" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B166" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015-A</t>
-        </is>
-      </c>
-      <c r="C166" s="22" t="inlineStr">
+      <c r="A166" s="25" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B166" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-636</t>
+        </is>
+      </c>
+      <c r="C166" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D166" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E166" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F166" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G166" s="21" t="n">
-        <v>4</v>
+      <c r="D166" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E166" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F166" s="25" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G166" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="21" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B167" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
-        </is>
-      </c>
-      <c r="C167" s="22" t="inlineStr">
+      <c r="A167" s="25" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B167" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1347</t>
+        </is>
+      </c>
+      <c r="C167" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D167" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E167" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F167" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G167" s="21" t="n">
+      <c r="D167" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E167" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F167" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G167" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="21" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B168" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-155-B</t>
-        </is>
-      </c>
-      <c r="C168" s="22" t="inlineStr">
+      <c r="A168" s="23" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B168" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-610</t>
+        </is>
+      </c>
+      <c r="C168" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D168" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E168" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F168" s="21" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G168" s="21" t="n">
+      <c r="D168" s="24" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E168" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F168" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="25" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B169" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015-E</t>
-        </is>
-      </c>
-      <c r="C169" s="26" t="inlineStr">
+      <c r="A169" s="23" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B169" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-600</t>
+        </is>
+      </c>
+      <c r="C169" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D169" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E169" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F169" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G169" s="25" t="n">
-        <v>11</v>
+      <c r="D169" s="24" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E169" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F169" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="25" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B170" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-E</t>
+          <t>US-OR-CRO-CRR-4S-D</t>
         </is>
       </c>
       <c r="C170" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D170" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E170" s="25" t="inlineStr">
@@ -7456,28 +7458,28 @@
         </is>
       </c>
       <c r="G170" s="25" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="25" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B171" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-D</t>
+          <t>US-OR-CRO-CRR-4SK-C</t>
         </is>
       </c>
       <c r="C171" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D171" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E171" s="25" t="inlineStr">
@@ -7491,28 +7493,28 @@
         </is>
       </c>
       <c r="G171" s="25" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="25" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B172" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-CRO-CRR-8SB</t>
         </is>
       </c>
       <c r="C172" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D172" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E172" s="25" t="inlineStr">
@@ -7522,32 +7524,32 @@
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="G172" s="25" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="25" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B173" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-CRO-CRR-8S-O</t>
         </is>
       </c>
       <c r="C173" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D173" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E173" s="25" t="inlineStr">
@@ -7557,32 +7559,32 @@
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="G173" s="25" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="25" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B174" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-149-B</t>
+          <t>US-OR-CRO-CRR-4S-L</t>
         </is>
       </c>
       <c r="C174" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D174" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E174" s="25" t="inlineStr">
@@ -7592,172 +7594,172 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G174" s="25" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B175" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-215-C</t>
-        </is>
-      </c>
-      <c r="C175" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D175" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E175" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F175" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G175" s="23" t="n">
-        <v>11</v>
+      <c r="A175" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B175" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SC-A</t>
+        </is>
+      </c>
+      <c r="C175" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D175" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E175" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F175" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G175" s="25" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B176" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-215-F</t>
-        </is>
-      </c>
-      <c r="C176" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D176" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E176" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F176" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G176" s="23" t="n">
-        <v>6</v>
+      <c r="A176" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B176" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SC</t>
+        </is>
+      </c>
+      <c r="C176" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D176" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E176" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F176" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G176" s="25" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B177" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-151-G</t>
-        </is>
-      </c>
-      <c r="C177" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D177" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E177" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F177" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G177" s="23" t="n">
-        <v>1</v>
+      <c r="A177" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B177" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SB-I</t>
+        </is>
+      </c>
+      <c r="C177" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D177" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E177" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F177" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G177" s="25" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="21" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B178" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
-        </is>
-      </c>
-      <c r="C178" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D178" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E178" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F178" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G178" s="21" t="n">
-        <v>4</v>
+      <c r="A178" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B178" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-K</t>
+        </is>
+      </c>
+      <c r="C178" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D178" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E178" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F178" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G178" s="25" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="25" t="inlineStr">
         <is>
-          <t>99362</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B179" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-039</t>
+          <t>US-OR-CRO-CRR-4SC-B</t>
         </is>
       </c>
       <c r="C179" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D179" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E179" s="25" t="inlineStr">
@@ -7767,137 +7769,137 @@
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G179" s="25" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="23" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B180" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C180" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D180" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E180" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F180" s="23" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G180" s="23" t="n">
-        <v>22</v>
+      <c r="A180" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B180" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SB-C</t>
+        </is>
+      </c>
+      <c r="C180" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D180" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E180" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F180" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G180" s="25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="21" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B181" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1713-B</t>
-        </is>
-      </c>
-      <c r="C181" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D181" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E181" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F181" s="21" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G181" s="21" t="n">
-        <v>1</v>
+      <c r="A181" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B181" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-F</t>
+        </is>
+      </c>
+      <c r="C181" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D181" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E181" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F181" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G181" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="21" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B182" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1713-A</t>
-        </is>
-      </c>
-      <c r="C182" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D182" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E182" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F182" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G182" s="21" t="n">
-        <v>1</v>
+      <c r="A182" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B182" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SB-J</t>
+        </is>
+      </c>
+      <c r="C182" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D182" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E182" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F182" s="25" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G182" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B183" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1707</t>
+          <t>US-OR-CRO-CRR-4S-N</t>
         </is>
       </c>
       <c r="C183" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D183" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E183" s="25" t="inlineStr">
@@ -7907,32 +7909,32 @@
       </c>
       <c r="F183" s="25" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G183" s="25" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B184" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1941</t>
+          <t>US-OR-CRO-CRR-4SB-G</t>
         </is>
       </c>
       <c r="C184" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D184" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E184" s="25" t="inlineStr">
@@ -7942,32 +7944,32 @@
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G184" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B185" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1956</t>
+          <t>US-OR-CRO-CRR-4SK-A</t>
         </is>
       </c>
       <c r="C185" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D185" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E185" s="25" t="inlineStr">
@@ -7977,347 +7979,347 @@
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G185" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B186" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-I</t>
+        </is>
+      </c>
+      <c r="C186" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D186" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E186" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F186" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G186" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B187" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SK-B</t>
+        </is>
+      </c>
+      <c r="C187" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D187" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E187" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F187" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G187" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B188" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-1S-Q</t>
+        </is>
+      </c>
+      <c r="C188" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D188" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E188" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F188" s="25" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G188" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B189" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-E</t>
+        </is>
+      </c>
+      <c r="C189" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D189" s="26" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E189" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F189" s="25" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G185" s="25" t="n">
+      <c r="G189" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B186" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-2261</t>
-        </is>
-      </c>
-      <c r="C186" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D186" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E186" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F186" s="23" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="G186" s="23" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B187" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1946</t>
-        </is>
-      </c>
-      <c r="C187" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D187" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E187" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F187" s="23" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="G187" s="23" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B188" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1701</t>
-        </is>
-      </c>
-      <c r="C188" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D188" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E188" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F188" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G188" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B189" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1361</t>
-        </is>
-      </c>
-      <c r="C189" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D189" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E189" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F189" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="190">
-      <c r="A190" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B190" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C190" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D190" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E190" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F190" s="21" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G190" s="21" t="n">
-        <v>29</v>
+      <c r="A190" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B190" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-8S-F</t>
+        </is>
+      </c>
+      <c r="C190" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D190" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E190" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F190" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G190" s="23" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B191" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140624S</t>
-        </is>
-      </c>
-      <c r="C191" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D191" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E191" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F191" s="21" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="G191" s="21" t="n">
-        <v>1</v>
+      <c r="A191" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B191" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-J</t>
+        </is>
+      </c>
+      <c r="C191" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D191" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E191" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F191" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B192" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C192" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D192" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E192" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F192" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G192" s="21" t="n">
-        <v>1</v>
+      <c r="A192" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B192" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-1S-J</t>
+        </is>
+      </c>
+      <c r="C192" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D192" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E192" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F192" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G192" s="23" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B193" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
-        </is>
-      </c>
-      <c r="C193" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D193" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E193" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F193" s="25" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G193" s="25" t="n">
-        <v>5</v>
+      <c r="A193" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B193" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-1S-K</t>
+        </is>
+      </c>
+      <c r="C193" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D193" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E193" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F193" s="23" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G193" s="23" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B194" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
-        </is>
-      </c>
-      <c r="C194" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D194" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E194" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F194" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G194" s="25" t="n">
-        <v>1</v>
+      <c r="A194" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B194" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-1S-F</t>
+        </is>
+      </c>
+      <c r="C194" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D194" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E194" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F194" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G194" s="23" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="23" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B195" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1497</t>
+          <t>US-OR-CRO-CRR-8SG-B</t>
         </is>
       </c>
       <c r="C195" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D195" s="24" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E195" s="23" t="inlineStr">
@@ -8327,32 +8329,32 @@
       </c>
       <c r="F195" s="23" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G195" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="23" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B196" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1505</t>
+          <t>US-OR-CRO-CRR-8S-T</t>
         </is>
       </c>
       <c r="C196" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D196" s="24" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E196" s="23" t="inlineStr">
@@ -8362,32 +8364,32 @@
       </c>
       <c r="F196" s="23" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G196" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="23" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B197" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1513</t>
+          <t>US-OR-CRO-CRR-8S-S</t>
         </is>
       </c>
       <c r="C197" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D197" s="24" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E197" s="23" t="inlineStr">
@@ -8397,32 +8399,32 @@
       </c>
       <c r="F197" s="23" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="G197" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="23" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B198" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1495</t>
+          <t>US-OR-CRO-CRR-4SB-D</t>
         </is>
       </c>
       <c r="C198" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D198" s="24" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E198" s="23" t="inlineStr">
@@ -8432,67 +8434,67 @@
       </c>
       <c r="F198" s="23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B199" s="22" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C199" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D199" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E199" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F199" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G199" s="21" t="n">
+      <c r="A199" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B199" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SB-E</t>
+        </is>
+      </c>
+      <c r="C199" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D199" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E199" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F199" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G199" s="23" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="23" t="inlineStr">
         <is>
-          <t>97023</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B200" s="24" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>US-OR-CRO-CRR-1S-M</t>
         </is>
       </c>
       <c r="C200" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D200" s="24" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Crook, Wheeler</t>
         </is>
       </c>
       <c r="E200" s="23" t="inlineStr">
@@ -8506,133 +8508,133 @@
         </is>
       </c>
       <c r="G200" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B201" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-8S-M</t>
+        </is>
+      </c>
+      <c r="C201" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D201" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E201" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F201" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G201" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B201" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1247</t>
-        </is>
-      </c>
-      <c r="C201" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D201" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E201" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F201" s="21" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="G201" s="21" t="n">
+    <row r="202">
+      <c r="A202" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B202" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-8S-I</t>
+        </is>
+      </c>
+      <c r="C202" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D202" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E202" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F202" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G202" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B202" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1246</t>
-        </is>
-      </c>
-      <c r="C202" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D202" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E202" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F202" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G202" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="203">
-      <c r="A203" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B203" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-636</t>
-        </is>
-      </c>
-      <c r="C203" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D203" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E203" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F203" s="25" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G203" s="25" t="n">
+      <c r="A203" s="23" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B203" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-090-A</t>
+        </is>
+      </c>
+      <c r="C203" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D203" s="24" t="inlineStr">
+        <is>
+          <t>Crook, Wheeler</t>
+        </is>
+      </c>
+      <c r="E203" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F203" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G203" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="25" t="inlineStr">
         <is>
-          <t>97814</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B204" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1347</t>
+          <t>Elk Mountain</t>
         </is>
       </c>
       <c r="C204" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D204" s="26" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E204" s="25" t="inlineStr">
@@ -8642,67 +8644,67 @@
       </c>
       <c r="F204" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="G204" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="23" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B205" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-610</t>
-        </is>
-      </c>
-      <c r="C205" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D205" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E205" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F205" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G205" s="23" t="n">
-        <v>1</v>
+      <c r="A205" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B205" s="26" t="inlineStr">
+        <is>
+          <t>Mill Creek Buttes</t>
+        </is>
+      </c>
+      <c r="C205" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D205" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E205" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F205" s="25" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G205" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="23" t="inlineStr">
         <is>
-          <t>97814</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B206" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-600</t>
+          <t>Cooper Spur North</t>
         </is>
       </c>
       <c r="C206" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D206" s="24" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E206" s="23" t="inlineStr">
@@ -8712,81 +8714,81 @@
       </c>
       <c r="F206" s="23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="G206" s="23" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="25" t="inlineStr">
+      <c r="A207" s="23" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B207" s="26" t="inlineStr">
-        <is>
-          <t>Elk Mountain</t>
-        </is>
-      </c>
-      <c r="C207" s="26" t="inlineStr">
+      <c r="B207" s="24" t="inlineStr">
+        <is>
+          <t>Cooper Spur South</t>
+        </is>
+      </c>
+      <c r="C207" s="24" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D207" s="26" t="inlineStr">
+      <c r="D207" s="24" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E207" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F207" s="25" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G207" s="25" t="n">
+      <c r="E207" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F207" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G207" s="23" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B208" s="24" t="inlineStr">
+        <is>
+          <t>Gibson Prairie</t>
+        </is>
+      </c>
+      <c r="C208" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D208" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E208" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F208" s="23" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G208" s="23" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B208" s="26" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C208" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D208" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E208" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F208" s="25" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G208" s="25" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -8797,7 +8799,7 @@
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>Cooper Spur North</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
@@ -8817,102 +8819,102 @@
       </c>
       <c r="F209" s="23" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G209" s="23" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="23" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B210" s="24" t="inlineStr">
-        <is>
-          <t>Cooper Spur South</t>
-        </is>
-      </c>
-      <c r="C210" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D210" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E210" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F210" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G210" s="23" t="n">
-        <v>63</v>
+      <c r="A210" s="25" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B210" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C210" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D210" s="26" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E210" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F210" s="25" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G210" s="25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="23" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B211" s="24" t="inlineStr">
-        <is>
-          <t>Gibson Prairie</t>
-        </is>
-      </c>
-      <c r="C211" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D211" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E211" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F211" s="23" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G211" s="23" t="n">
-        <v>4</v>
+      <c r="A211" s="25" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B211" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1450</t>
+        </is>
+      </c>
+      <c r="C211" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D211" s="26" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E211" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F211" s="25" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G211" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="23" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B212" s="24" t="inlineStr">
         <is>
-          <t>White River</t>
+          <t>US-OR-UNI-UCO-1421</t>
         </is>
       </c>
       <c r="C212" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D212" s="24" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E212" s="23" t="inlineStr">
@@ -8922,81 +8924,81 @@
       </c>
       <c r="F212" s="23" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G212" s="23" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="25" t="inlineStr">
+      <c r="A213" s="23" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B213" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1435</t>
-        </is>
-      </c>
-      <c r="C213" s="26" t="inlineStr">
+      <c r="B213" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1436</t>
+        </is>
+      </c>
+      <c r="C213" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D213" s="26" t="inlineStr">
+      <c r="D213" s="24" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E213" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F213" s="25" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="G213" s="25" t="n">
-        <v>6</v>
+      <c r="E213" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F213" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G213" s="23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="25" t="inlineStr">
+      <c r="A214" s="23" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B214" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C214" s="26" t="inlineStr">
+      <c r="B214" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1437</t>
+        </is>
+      </c>
+      <c r="C214" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D214" s="26" t="inlineStr">
+      <c r="D214" s="24" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E214" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F214" s="25" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G214" s="25" t="n">
-        <v>1</v>
+      <c r="E214" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F214" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G214" s="23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="215">
@@ -9007,7 +9009,7 @@
       </c>
       <c r="B215" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C215" s="24" t="inlineStr">
@@ -9027,67 +9029,67 @@
       </c>
       <c r="F215" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G215" s="23" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="23" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B216" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1436</t>
-        </is>
-      </c>
-      <c r="C216" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D216" s="24" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E216" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F216" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G216" s="23" t="n">
-        <v>9</v>
+      <c r="A216" s="25" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B216" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1941</t>
+        </is>
+      </c>
+      <c r="C216" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D216" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E216" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F216" s="25" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G216" s="25" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="23" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B217" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-KLA-KLA-2261</t>
         </is>
       </c>
       <c r="C217" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D217" s="24" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E217" s="23" t="inlineStr">
@@ -9097,32 +9099,32 @@
       </c>
       <c r="F217" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G217" s="23" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="23" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B218" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1438</t>
+          <t>US-OR-KLA-KLA-1936</t>
         </is>
       </c>
       <c r="C218" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D218" s="24" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E218" s="23" t="inlineStr">
@@ -9132,46 +9134,46 @@
       </c>
       <c r="F218" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G218" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="25" t="inlineStr">
+      <c r="A219" s="23" t="inlineStr">
         <is>
           <t>97603</t>
         </is>
       </c>
-      <c r="B219" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C219" s="26" t="inlineStr">
+      <c r="B219" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2256</t>
+        </is>
+      </c>
+      <c r="C219" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D219" s="26" t="inlineStr">
+      <c r="D219" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E219" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F219" s="25" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="G219" s="25" t="n">
-        <v>15</v>
+      <c r="E219" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F219" s="23" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G219" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -9182,7 +9184,7 @@
       </c>
       <c r="B220" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C220" s="24" t="inlineStr">
@@ -9202,11 +9204,11 @@
       </c>
       <c r="F220" s="23" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G220" s="23" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9217,7 +9219,7 @@
       </c>
       <c r="B221" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1936</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C221" s="24" t="inlineStr">
@@ -9237,102 +9239,102 @@
       </c>
       <c r="F221" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G221" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="23" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B222" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-2256</t>
-        </is>
-      </c>
-      <c r="C222" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D222" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E222" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F222" s="23" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="G222" s="23" t="n">
-        <v>1</v>
+      <c r="A222" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B222" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C222" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D222" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E222" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F222" s="25" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G222" s="25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="23" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B223" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C223" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D223" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E223" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F223" s="23" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G223" s="23" t="n">
+      <c r="A223" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B223" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-121-B</t>
+        </is>
+      </c>
+      <c r="C223" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D223" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E223" s="25" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F223" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G223" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="23" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B224" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1701</t>
+          <t>US-OR-UMA-UMC-032</t>
         </is>
       </c>
       <c r="C224" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D224" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E224" s="23" t="inlineStr">
@@ -9342,137 +9344,137 @@
       </c>
       <c r="F224" s="23" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G224" s="23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="23" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B225" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-123-B</t>
+        </is>
+      </c>
+      <c r="C225" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D225" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E225" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F225" s="23" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="G225" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="25" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="23" t="inlineStr">
         <is>
           <t>97862</t>
         </is>
       </c>
-      <c r="B225" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C225" s="26" t="inlineStr">
+      <c r="B226" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406025-B</t>
+        </is>
+      </c>
+      <c r="C226" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D225" s="26" t="inlineStr">
+      <c r="D226" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E225" s="25" t="inlineStr">
+      <c r="E226" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F226" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G226" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="25" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B227" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C227" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D227" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E227" s="25" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F225" s="25" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="G225" s="25" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="25" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B226" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C226" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D226" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E226" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F226" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G226" s="25" t="n">
+      <c r="F227" s="25" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G227" s="25" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="23" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B227" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C227" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D227" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E227" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F227" s="23" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="G227" s="23" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="23" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="B228" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-B</t>
+          <t>BC1</t>
         </is>
       </c>
       <c r="C228" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Burnt Creek Fire</t>
         </is>
       </c>
       <c r="D228" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Wallowa</t>
         </is>
       </c>
       <c r="E228" s="23" t="inlineStr">
@@ -9482,32 +9484,32 @@
       </c>
       <c r="F228" s="23" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="G228" s="23" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="23" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="B229" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
+          <t>WRR</t>
         </is>
       </c>
       <c r="C229" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D229" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E229" s="23" t="inlineStr">
@@ -9517,67 +9519,67 @@
       </c>
       <c r="F229" s="23" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="G229" s="23" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="25" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B230" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
-        </is>
-      </c>
-      <c r="C230" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D230" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E230" s="25" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F230" s="25" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G230" s="25" t="n">
-        <v>1</v>
+      <c r="A230" s="23" t="inlineStr">
+        <is>
+          <t>97058</t>
+        </is>
+      </c>
+      <c r="B230" s="24" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="C230" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D230" s="24" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E230" s="23" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F230" s="23" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G230" s="23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="23" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B231" s="24" t="inlineStr">
         <is>
-          <t>BC1</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C231" s="24" t="inlineStr">
         <is>
-          <t>Burnt Creek Fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D231" s="24" t="inlineStr">
         <is>
-          <t>Wallowa</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E231" s="23" t="inlineStr">
@@ -9587,32 +9589,32 @@
       </c>
       <c r="F231" s="23" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="G231" s="23" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="23" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B232" s="24" t="inlineStr">
         <is>
-          <t>WRR</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C232" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D232" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E232" s="23" t="inlineStr">
@@ -9622,32 +9624,32 @@
       </c>
       <c r="F232" s="23" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G232" s="23" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="23" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B233" s="24" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C233" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D233" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E233" s="23" t="inlineStr">
@@ -9657,32 +9659,32 @@
       </c>
       <c r="F233" s="23" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G233" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="23" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B234" s="24" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>US-OR-WHE-WHH-090-A</t>
         </is>
       </c>
       <c r="C234" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D234" s="24" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Wheeler</t>
         </is>
       </c>
       <c r="E234" s="23" t="inlineStr">
@@ -9692,32 +9694,32 @@
       </c>
       <c r="F234" s="23" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G234" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="23" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B235" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C235" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D235" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E235" s="23" t="inlineStr">
@@ -9727,22 +9729,22 @@
       </c>
       <c r="F235" s="23" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G235" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="23" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="B236" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C236" s="24" t="inlineStr">
@@ -9762,120 +9764,15 @@
       </c>
       <c r="F236" s="23" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G236" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B237" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-090-A</t>
-        </is>
-      </c>
-      <c r="C237" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D237" s="24" t="inlineStr">
-        <is>
-          <t>Wheeler</t>
-        </is>
-      </c>
-      <c r="E237" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F237" s="23" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G237" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="23" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B238" s="24" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C238" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D238" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E238" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F238" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G238" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="23" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="B239" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C239" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D239" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E239" s="23" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F239" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G239" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" ht="60" customHeight="1">
-      <c r="A241" s="27" t="inlineStr">
+    <row r="238" ht="60" customHeight="1">
+      <c r="A238" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -9883,8 +9780,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A238:G238"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A241:G241"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
